--- a/output/pdf_financials_xlsx/CP.xlsx
+++ b/output/pdf_financials_xlsx/CP.xlsx
@@ -10092,7 +10092,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">

--- a/output/pdf_financials_xlsx/CP.xlsx
+++ b/output/pdf_financials_xlsx/CP.xlsx
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>13154</v>
+        <v>13315</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>14777</v>
+        <v>14939</v>
       </c>
     </row>
     <row r="62">
@@ -2613,16 +2613,14 @@
       <c r="E67" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F67" s="3" t="n">
+        <v>245</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>325</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>343</v>
       </c>
     </row>
     <row r="68">
@@ -5847,7 +5845,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -7232,7 +7230,11 @@
           <t>Goodwill and intangible assets (Note 17) 189.8</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -8529,7 +8531,11 @@
           <t>Goodwill and intangible assets (Note 17) 202.3</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
